--- a/MatriceVer7/PRAKTIK-AI_Matrice_kurzu_v7.0.xlsx
+++ b/MatriceVer7/PRAKTIK-AI_Matrice_kurzu_v7.0.xlsx
@@ -8352,7 +8352,7 @@
       </c>
       <c r="E5" s="73" t="inlineStr">
         <is>
-          <t>Akademik: akademický pracovník vysoké školy – vyučující, výzkumník nebo doktorand (Ph.D.). Typické pracovní situace: příprava a vedení výuky; zadávání a hodnocení studentských prací; vedení a oponování závěrečných prací; výzkum, analýza dat a rešerše; psaní odborných textů, grantových přihlášek a posudků; recenzní řízení. Doktorand je zároveň studující: kromě výzkumu a výuky se ho týká i disertační práce a její deklarace využití AI. Pravidla, která se na skupinu vztahují: vnitřní předpisy univerzity v části pro vyučující a zaměstnance, publikační etika, pravidla časopisů a poskytovatelů grantů. Pravidla pro studentské práce na akademiky nepřenášej; výjimkou je disertační práce doktoranda. Oslovení: vykání; v textu podle situace „vyučující", „výzkumník", „doktorand". Odborný akademický jazyk je přiměřený na každé úrovni – úroveň pokročilosti se týká zkušenosti s AI, ne odbornosti v oboru.</t>
+          <t>Akademik: akademický pracovník vysoké školy – vyučující, výzkumník nebo doktorand (Ph.D.). Typické pracovní situace: příprava a vedení výuky; zadávání a hodnocení studentských prací; vedení a oponování závěrečných prací; výzkum, analýza dat a rešerše; psaní odborných textů, grantových přihlášek a posudků; recenzní řízení. Doktorand je zároveň studující: kromě výzkumu a výuky se ho týká i disertační práce a její deklarace využití AI. Pravidla, která se na skupinu vztahují: vnitřní předpisy univerzity v části pro vyučující a zaměstnance, publikační etika, pravidla časopisů a poskytovatelů grantů. Pravidla pro studentské práce na akademiky nepřenášej; výjimkou je disertační práce doktoranda. Oslovení: vykání; osobu neoznačuj rodově – piš „vyučující", případně popisem činnosti („ve výzkumu", „při vedení práce", „v disertaci"). Odborný akademický jazyk je přiměřený na každé úrovni – úroveň pokročilosti se týká zkušenosti s AI, ne odbornosti v oboru.</t>
         </is>
       </c>
     </row>
